--- a/employee_surveys/011_tester_accountability_survey--employee_surveys.xlsx
+++ b/employee_surveys/011_tester_accountability_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>test_cycle_status</t>
+          <t>Test Cycle Status</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,14 +548,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>blockers</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>List the blockers that prevented you from completing this test cycle</t>
-        </is>
-      </c>
+          <t>Blockers</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -575,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>test_cycle_comments</t>
+          <t>Test Cycle Comments</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -598,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>self_assessed_accountability</t>
+          <t>Self-Assessed Accountability</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -621,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>manager_assessed_accountability</t>
+          <t>Manager-Assessed Accountability</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -639,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>blockers</t>
+          <t>blockers_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>blockers</t>
+          <t>Blockers 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -662,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>test_cycle_status</t>
+          <t>test_cycle_status_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>test_cycle_status</t>
+          <t>Test Cycle Status 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>test_cycle_comments</t>
+          <t>test_cycle_comments_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>test_cycle_comments</t>
+          <t>Test Cycle Comments 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,23 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>blockers</t>
+          <t>test_cycle_status_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>blockers</t>
+          <t>Test Cycle Status 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -736,13 +732,82 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>manager_comments</t>
+          <t>Manager Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>did_the_test_cycle_meet_its_goals</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Has the test cycle met its goals?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>biggest_challenges_faced_during_the_test_cycle</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What were the biggest challenges faced during the test cycle?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prepared_for_test_cycle</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Prepared For Test Cycle</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -757,10 +822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
@@ -836,7 +901,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>blockers_choices</t>
+          <t>blockers_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -853,7 +918,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>blockers_choices</t>
+          <t>blockers_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -870,7 +935,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>blockers_choices</t>
+          <t>blockers_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -887,7 +952,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>blockers_choices</t>
+          <t>blockers_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -904,7 +969,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>blockers_choices</t>
+          <t>blockers_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -921,7 +986,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>blockers_choices</t>
+          <t>blockers_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -932,6 +997,108 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>blocker6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>test_cycle_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>test_cycle_in_progress</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Test Cycle In Progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>test_cycle_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>on_hold</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>test_cycle_status_3_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>biggest_challenges_faced_during_the_test_cycle_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>biggest_challenges_faced_during_the_test_cycle_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>biggest_challenges_faced_during_the_test_cycle_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
